--- a/docs/CPQ_OffTopic_Intent_Failed_Testcases_RootCause_Fix_2026-08-13.xlsx
+++ b/docs/CPQ_OffTopic_Intent_Failed_Testcases_RootCause_Fix_2026-08-13.xlsx
@@ -10,6 +10,7 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Summary" sheetId="1" state="visible" r:id="rId1"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="10-OffTopic" sheetId="2" state="visible" r:id="rId2"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="4-Intent" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Followup-LLM-First-Coverage" sheetId="4" state="visible" r:id="rId4"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -19,7 +20,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="2">
+  <fonts count="3">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -31,8 +32,11 @@
       <b val="1"/>
       <color rgb="00FFFFFF"/>
     </font>
+    <font>
+      <b val="1"/>
+    </font>
   </fonts>
-  <fills count="6">
+  <fills count="7">
     <fill>
       <patternFill/>
     </fill>
@@ -57,6 +61,11 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="00FFF3CD"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00DDEBF7"/>
       </patternFill>
     </fill>
   </fills>
@@ -86,7 +95,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="6">
+  <cellXfs count="8">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -99,6 +108,12 @@
       <alignment vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -552,9 +567,6 @@
           <t>https://github.com/Giggso-Inc/aryx-enterprise/pull/new/fix/cpq-offtopic-approval-qa-false-positives</t>
         </is>
       </c>
-      <c r="C4" t="inlineStr"/>
-      <c r="D4" t="inlineStr"/>
-      <c r="E4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -567,9 +579,6 @@
           <t>fix/cpq-offtopic-approval-qa-false-positives</t>
         </is>
       </c>
-      <c r="C5" t="inlineStr"/>
-      <c r="D5" t="inlineStr"/>
-      <c r="E5" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -4498,4 +4507,130 @@
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:B9"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="26" customWidth="1" min="1" max="1"/>
+    <col width="110" customWidth="1" min="2" max="2"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="2" t="inlineStr">
+        <is>
+          <t>Item</t>
+        </is>
+      </c>
+      <c r="B1" s="2" t="inlineStr">
+        <is>
+          <t>Detail</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="6" t="inlineStr">
+        <is>
+          <t>PR / Branch</t>
+        </is>
+      </c>
+      <c r="B2" s="7" t="inlineStr">
+        <is>
+          <t>fix/cpq-approval-llm-first-coverage-proof (aryx-enterprise, base dev-rv)</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="6" t="inlineStr">
+        <is>
+          <t>Question raised</t>
+        </is>
+      </c>
+      <c r="B3" s="7" t="inlineStr">
+        <is>
+          <t>Does the regex-only fix (previous PR) generalize to any phrasing, or does it only cover the exact reported test cases?</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="6" t="inlineStr">
+        <is>
+          <t>Issue</t>
+        </is>
+      </c>
+      <c r="B4" s="7" t="inlineStr">
+        <is>
+          <t>detect_approval/detect_qa_question (engine.py) are pure anchored regex with no semantic fallback. Regex is an enumeration -- it cannot cover every way a customer phrases approval ("sounds good to me", "works for me"). The D42 fix (narrowing great/perfect to a whole-message-only pattern) also introduced a new gap: "Perfect, let's go" no longer matches the regex either.</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="6" t="inlineStr">
+        <is>
+          <t>Root Cause</t>
+        </is>
+      </c>
+      <c r="B5" s="7" t="inlineStr">
+        <is>
+          <t>No LLM-based fallback existed for these two detectors at the point they are consulted directly -- unlike other categories already migrated to intent_gateway.py's LLM-first classifier.</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="6" t="inlineStr">
+        <is>
+          <t>Fix Implemented</t>
+        </is>
+      </c>
+      <c r="B6" s="7" t="inlineStr">
+        <is>
+          <t>Investigated adding a NEW LLM-fallback helper (the originally recommended approach) and found it unnecessary: APPROVAL and QA_QUESTION are ALREADY wired into _dispatch_intent_result (ask_api.py, commits 06d4c69 / b7151cc) as no-target, non-mutating categories -- classify_intent's quarantine (confidence=HIGH + evidence_span present) is the only gate, no dependency on the regex at all, and cpq_llm_first_enabled defaults to True. Added 3 tests proving this coverage instead of duplicating existing infrastructure: 2 in tests/test_cpq_intent_gateway.py (classify_intent resolves 'sounds good to me...' and 'Perfect, let's go' to APPROVAL/HIGH) and 1 integration test in tests/test_cpq_2026_07_28_fixes.py proving _dispatch_intent_result's APPROVAL branch submits the payload with detect_approval patched to return False.</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="6" t="inlineStr">
+        <is>
+          <t>Known gap NOT closed</t>
+        </is>
+      </c>
+      <c r="B7" s="7" t="inlineStr">
+        <is>
+          <t>session.guided_mode=True skips the LLM-first gateway entirely (ask_api.py STEP-6 gate) -- guided-mode sessions still rely solely on the regex for approval detection.</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="6" t="inlineStr">
+        <is>
+          <t>Independent review findings (all fixed)</t>
+        </is>
+      </c>
+      <c r="B8" s="7" t="inlineStr">
+        <is>
+          <t>HIGH: a test asserted engine.detect_approval.assert_not_called() as proof the LLM path skips the regex, but intent_gateway.py never calls that method for ANY category -- tautological, not evidence. Replaced with a real integration test at the correct call site. MEDIUM: the guided_mode gap was undocumented -- now documented. LOW: 2 new tests left engine.detect_change_* mocks unset, unlike file convention -- fixed.</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="6" t="inlineStr">
+        <is>
+          <t>Verification</t>
+        </is>
+      </c>
+      <c r="B9" s="7" t="inlineStr">
+        <is>
+          <t>tests/test_cpq_intent_gateway.py: 25 passed. tests/test_cpq_2026_07_28_fixes.py -k approval: 7 passed. (Full file has pre-existing, unrelated tests that hang in this sandbox due to a real network-access limitation, confirmed via bisection to predate and be unrelated to this change.)</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
 </file>
--- a/docs/CPQ_OffTopic_Intent_Failed_Testcases_RootCause_Fix_2026-08-13.xlsx
+++ b/docs/CPQ_OffTopic_Intent_Failed_Testcases_RootCause_Fix_2026-08-13.xlsx
@@ -552,9 +552,6 @@
           <t>https://github.com/Giggso-Inc/aryx-enterprise/pull/new/fix/cpq-offtopic-approval-qa-false-positives</t>
         </is>
       </c>
-      <c r="C4" t="inlineStr"/>
-      <c r="D4" t="inlineStr"/>
-      <c r="E4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -567,9 +564,6 @@
           <t>fix/cpq-offtopic-approval-qa-false-positives</t>
         </is>
       </c>
-      <c r="C5" t="inlineStr"/>
-      <c r="D5" t="inlineStr"/>
-      <c r="E5" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -3320,7 +3314,7 @@
       </c>
       <c r="K44" s="4" t="inlineStr">
         <is>
-          <t>Moved great/perfect out of the general alternation into a standalone-reply-only pattern: ^(?:great|perfect)\s*[!.]*$ -- only matches when the entire trimmed message IS just that word (+ optional punctuation).</t>
+          <t>Moved great/perfect out of the general alternation into a standalone-reply-only pattern: ^(?:great|perfect)\s*[!.]*$ -- only matches when the entire trimmed message IS just that word (+ optional punctuation). UPDATE (raven review on PR #192): this whole-message-only pattern also broke previously-working combined phrasings ('Great, let's go', 'Perfect, that works') that the pre-fix regex used to match -- a real regression for session.guided_mode=True sessions (which never reach the LLM-first gateway fallback). Fixed: loosened to ^(?:great|perfect)\b[\s,!.]*(?:let'?s?\s+go|that'?s?\s+(?:works|good|right))?$ -- restores the combined phrasings, keeps the original false-positive rejection intact. 2 pinning tests added in tests/test_cpq_post_approval_activation.py.</t>
         </is>
       </c>
       <c r="L44" s="4" t="inlineStr">
